--- a/annotation/analysis/survey/export/agreed_feature_four_expert.xlsx
+++ b/annotation/analysis/survey/export/agreed_feature_four_expert.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bay1977\Code\cdl-inflation-narrative\annotation\analysis\survey\export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mw001\Code\cdl-inflation-narrative\annotation\analysis\survey\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF88344F-E356-49D4-9318-CA47111DBD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5ABA8A-4A97-4910-BA58-D0453ED86203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -4689,9 +4686,6 @@
     <t>('Inflation', '()', 'Inflation'); ('Löhne', '()', 'Inflation')</t>
   </si>
   <si>
-    <t>('Politisches Missmanagement', '()', 'Hohe Energiepreise'); ('Hohe Energiepreise', '()', 'Inflation'); ('Ökonomische Krise', '()', 'Löhne'); ('Löhne', '()', 'Inflation')</t>
-  </si>
-  <si>
     <t>Pandemie/Covid - Aufgrund des weltweiten Lockdowns kam es zu Produktions- und Lieferengpässen vieler Waren und Dienstleistungen, was die Preise in die Höhe getrieben hat. - inflation.</t>
   </si>
   <si>
@@ -5229,9 +5223,6 @@
     <t>Die sanktionen gegen russland, Die klimaabgaben bzw gesetze dazu - Durch die sanktionen hat sich alles verteuert, genauso durch die abschaltung der atomkraftwerke und in folge dessen zu wenig stromproduktion - inflation.</t>
   </si>
   <si>
-    <t>('Klimawandel', '()', 'Inflation'); ('Klimawandel', '()', 'Steuererhöhungen'); ('Steuererhöhungen', '()', 'Inflation'); ('Hohe Energiepreise', '()', 'Inflation'); ('Geldpolitik', '()', 'Inflation'); ('Steuererhöhungen', '()', 'Klimawandel')</t>
-  </si>
-  <si>
     <t>('Klimawandel', '()', 'Inflation'); ('Angebot (Rest)', '()', 'Inflation'); ('Politisches Missmanagement', '()', 'Angebot (Rest)'); ('Geopolitik', '()', 'Inflation'); ('Steuererhöhungen', '()', 'Klimawandel')</t>
   </si>
   <si>
@@ -5285,9 +5276,6 @@
     <t>Preise für Nahrungsmittel, Gestiegene Energiekosten - Hauptverantwortlich dafür war die Entwicklung der Erdgaspreise. - inflation.</t>
   </si>
   <si>
-    <t>('Lebensmittelpreise', '()', 'Inflation'); ('Hohe Energiepreise', '()', 'Lebensmittelpreise'); ('Lebensmittelpreise', '()', 'Lebensmittelpreise')</t>
-  </si>
-  <si>
     <t>('Inflation', '()', 'Lebensmittelpreise'); ('Inflation', '()', 'Hohe Energiepreise')</t>
   </si>
   <si>
@@ -5463,9 +5451,6 @@
   </si>
   <si>
     <t>Rohölpreise, &lt;Knappheit von Rohstoffen, Steigende Exporte, Schlechte Wetterlage in einigen Laändetrn, Steigende Löhne - Durch die gleichzeitigen bedingten Lohnerhöhungen, müssen auch Wirtschaftlich gesehen die Endpreise steigen. - inflation.</t>
-  </si>
-  <si>
-    <t>('Klimawandel', '()', 'Inflation'); ('Export', '()', 'Inflation'); ('Inflation', '()', 'Inflation'); ('Löhne', '()', 'Inflation'); ('Angebot (Rest)', '()', 'Inflation')</t>
   </si>
   <si>
     <t>Energiepreise, schlechte Ernte durch Klima, Ukraine Krieg - Energiepreise sind stark angestiegen, dadurch mehr Kosten in der Produktion und Lagerung sowie Transport. - inflation.</t>
@@ -5607,6 +5592,18 @@
   </si>
   <si>
     <t xml:space="preserve">('Ökonomische Krise', '()', 'Inflation'); ('Angebot (Rest)', '()', 'Inflation'); </t>
+  </si>
+  <si>
+    <t>('Politisches Missmanagement', '()', 'Hohe Energiepreise'); ('Hohe Energiepreise', '()', 'Inflation');  ('Löhne', '()', 'Inflation')</t>
+  </si>
+  <si>
+    <t>('Klimawandel', '()', 'Inflation'); ('Klimawandel', '()', 'Steuererhöhungen'); ('Steuererhöhungen', '()', 'Inflation'); ('Hohe Energiepreise', '()', 'Inflation');  ('Steuererhöhungen', '()', 'Klimawandel')</t>
+  </si>
+  <si>
+    <t>('Lebensmittelpreise', '()', 'Inflation'); ('Hohe Energiepreise', '()', 'Lebensmittelpreise');</t>
+  </si>
+  <si>
+    <t>('Klimawandel', '()', 'Inflation'); ('Export', '()', 'Inflation'); ('Löhne', '()', 'Inflation'); ('Angebot (Rest)', '()', 'Inflation')</t>
   </si>
 </sst>
 </file>
@@ -5985,7 +5982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G724"/>
+  <dimension ref="A1:G722"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="49.85546875" style="3" customWidth="1"/>
@@ -12554,7 +12551,7 @@
         <v>860</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="E311" t="s">
         <v>861</v>
@@ -13280,7 +13277,7 @@
         <v>945</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>946</v>
@@ -14073,7 +14070,7 @@
         <v>1035</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="E385" t="s">
         <v>1036</v>
@@ -16066,7 +16063,7 @@
         <v>1266</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="E480" t="s">
         <v>294</v>
@@ -16198,7 +16195,7 @@
         <v>238</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="E486" t="s">
         <v>85</v>
@@ -18295,6 +18292,9 @@
       <c r="F587" t="s">
         <v>11</v>
       </c>
+      <c r="G587">
+        <v>20</v>
+      </c>
     </row>
     <row r="588" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A588">
@@ -18315,6 +18315,9 @@
       <c r="F588" t="s">
         <v>11</v>
       </c>
+      <c r="G588">
+        <v>20</v>
+      </c>
     </row>
     <row r="589" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A589">
@@ -18335,6 +18338,9 @@
       <c r="F589" t="s">
         <v>11</v>
       </c>
+      <c r="G589">
+        <v>21</v>
+      </c>
     </row>
     <row r="590" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A590">
@@ -18355,6 +18361,9 @@
       <c r="F590" t="s">
         <v>11</v>
       </c>
+      <c r="G590">
+        <v>20</v>
+      </c>
     </row>
     <row r="591" spans="1:7" ht="225" x14ac:dyDescent="0.25">
       <c r="A591">
@@ -18375,6 +18384,9 @@
       <c r="F591" t="s">
         <v>11</v>
       </c>
+      <c r="G591">
+        <v>20</v>
+      </c>
     </row>
     <row r="592" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A592">
@@ -18412,6 +18424,9 @@
       <c r="F593" t="s">
         <v>11</v>
       </c>
+      <c r="G593">
+        <v>21</v>
+      </c>
     </row>
     <row r="594" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A594">
@@ -18432,8 +18447,11 @@
       <c r="F594" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="595" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="G594">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>754</v>
       </c>
@@ -18444,13 +18462,16 @@
         <v>1537</v>
       </c>
       <c r="D595" s="3" t="s">
-        <v>1538</v>
+        <v>1836</v>
       </c>
       <c r="E595" t="s">
         <v>556</v>
       </c>
       <c r="F595" t="s">
         <v>11</v>
+      </c>
+      <c r="G595">
+        <v>21</v>
       </c>
     </row>
     <row r="596" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -18458,19 +18479,22 @@
         <v>755</v>
       </c>
       <c r="B596" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C596" s="3" t="s">
         <v>1539</v>
       </c>
-      <c r="C596" s="3" t="s">
+      <c r="D596" s="3" t="s">
         <v>1540</v>
       </c>
-      <c r="D596" s="3" t="s">
+      <c r="E596" t="s">
         <v>1541</v>
       </c>
-      <c r="E596" t="s">
-        <v>1542</v>
-      </c>
       <c r="F596" t="s">
         <v>11</v>
+      </c>
+      <c r="G596">
+        <v>20</v>
       </c>
     </row>
     <row r="597" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -18478,7 +18502,7 @@
         <v>758</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="E597" t="s">
         <v>93</v>
@@ -18495,7 +18519,7 @@
         <v>759</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="E598" t="s">
         <v>176</v>
@@ -18512,19 +18536,22 @@
         <v>760</v>
       </c>
       <c r="B599" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C599" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="C599" s="3" t="s">
+      <c r="D599" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="D599" s="3" t="s">
+      <c r="E599" t="s">
         <v>1547</v>
       </c>
-      <c r="E599" t="s">
-        <v>1548</v>
-      </c>
       <c r="F599" t="s">
         <v>11</v>
+      </c>
+      <c r="G599">
+        <v>20</v>
       </c>
     </row>
     <row r="600" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -18532,19 +18559,22 @@
         <v>761</v>
       </c>
       <c r="B600" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C600" s="3" t="s">
         <v>1549</v>
       </c>
-      <c r="C600" s="3" t="s">
+      <c r="D600" s="3" t="s">
         <v>1550</v>
-      </c>
-      <c r="D600" s="3" t="s">
-        <v>1551</v>
       </c>
       <c r="E600" t="s">
         <v>85</v>
       </c>
       <c r="F600" t="s">
         <v>11</v>
+      </c>
+      <c r="G600">
+        <v>20</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
@@ -18552,7 +18582,7 @@
         <v>762</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="E601" t="s">
         <v>138</v>
@@ -18569,19 +18599,22 @@
         <v>763</v>
       </c>
       <c r="B602" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C602" s="3" t="s">
         <v>1553</v>
       </c>
-      <c r="C602" s="3" t="s">
+      <c r="D602" s="3" t="s">
         <v>1554</v>
-      </c>
-      <c r="D602" s="3" t="s">
-        <v>1555</v>
       </c>
       <c r="E602" t="s">
         <v>294</v>
       </c>
       <c r="F602" t="s">
         <v>11</v>
+      </c>
+      <c r="G602">
+        <v>21</v>
       </c>
     </row>
     <row r="603" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -18589,7 +18622,7 @@
         <v>764</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="E603" t="s">
         <v>21</v>
@@ -18606,7 +18639,7 @@
         <v>765</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="E604" t="s">
         <v>837</v>
@@ -18623,7 +18656,7 @@
         <v>766</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="E605" t="s">
         <v>140</v>
@@ -18640,7 +18673,7 @@
         <v>768</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="E606" t="s">
         <v>37</v>
@@ -18657,7 +18690,7 @@
         <v>769</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E607" t="s">
         <v>1481</v>
@@ -18674,19 +18707,22 @@
         <v>770</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="C608" s="3" t="s">
         <v>114</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E608" t="s">
         <v>58</v>
       </c>
       <c r="F608" t="s">
         <v>11</v>
+      </c>
+      <c r="G608">
+        <v>20</v>
       </c>
     </row>
     <row r="609" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -18694,7 +18730,7 @@
         <v>771</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="E609" t="s">
         <v>837</v>
@@ -18711,19 +18747,22 @@
         <v>773</v>
       </c>
       <c r="B610" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C610" s="3" t="s">
         <v>1564</v>
       </c>
-      <c r="C610" s="3" t="s">
+      <c r="D610" s="3" t="s">
         <v>1565</v>
       </c>
-      <c r="D610" s="3" t="s">
+      <c r="E610" t="s">
         <v>1566</v>
       </c>
-      <c r="E610" t="s">
-        <v>1567</v>
-      </c>
       <c r="F610" t="s">
         <v>11</v>
+      </c>
+      <c r="G610">
+        <v>21</v>
       </c>
     </row>
     <row r="611" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -18731,19 +18770,22 @@
         <v>776</v>
       </c>
       <c r="B611" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C611" s="3" t="s">
         <v>1568</v>
       </c>
-      <c r="C611" s="3" t="s">
+      <c r="D611" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="D611" s="3" t="s">
-        <v>1570</v>
-      </c>
       <c r="E611" t="s">
         <v>21</v>
       </c>
       <c r="F611" t="s">
         <v>11</v>
+      </c>
+      <c r="G611">
+        <v>20</v>
       </c>
     </row>
     <row r="612" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -18751,10 +18793,10 @@
         <v>777</v>
       </c>
       <c r="B612" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E612" t="s">
         <v>1571</v>
-      </c>
-      <c r="E612" t="s">
-        <v>1572</v>
       </c>
       <c r="F612" t="s">
         <v>22</v>
@@ -18768,7 +18810,7 @@
         <v>778</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="E613" t="s">
         <v>382</v>
@@ -18785,7 +18827,7 @@
         <v>779</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C614" s="3" t="s">
         <v>663</v>
@@ -18798,6 +18840,9 @@
       </c>
       <c r="F614" t="s">
         <v>11</v>
+      </c>
+      <c r="G614">
+        <v>21</v>
       </c>
     </row>
     <row r="615" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -18805,19 +18850,22 @@
         <v>781</v>
       </c>
       <c r="B615" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C615" s="3" t="s">
         <v>1575</v>
       </c>
-      <c r="C615" s="3" t="s">
+      <c r="D615" s="3" t="s">
         <v>1576</v>
-      </c>
-      <c r="D615" s="3" t="s">
-        <v>1577</v>
       </c>
       <c r="E615" t="s">
         <v>26</v>
       </c>
       <c r="F615" t="s">
         <v>11</v>
+      </c>
+      <c r="G615">
+        <v>21</v>
       </c>
     </row>
     <row r="616" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -18825,10 +18873,10 @@
         <v>783</v>
       </c>
       <c r="B616" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C616" s="3" t="s">
         <v>1578</v>
-      </c>
-      <c r="C616" s="3" t="s">
-        <v>1579</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>50</v>
@@ -18845,7 +18893,7 @@
         <v>785</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E617" t="s">
         <v>37</v>
@@ -18862,19 +18910,22 @@
         <v>787</v>
       </c>
       <c r="B618" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C618" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="C618" s="3" t="s">
+      <c r="D618" s="3" t="s">
         <v>1582</v>
       </c>
-      <c r="D618" s="3" t="s">
+      <c r="E618" t="s">
         <v>1583</v>
       </c>
-      <c r="E618" t="s">
-        <v>1584</v>
-      </c>
       <c r="F618" t="s">
         <v>11</v>
+      </c>
+      <c r="G618">
+        <v>21</v>
       </c>
     </row>
     <row r="619" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -18882,7 +18933,7 @@
         <v>789</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="E619" t="s">
         <v>85</v>
@@ -18899,19 +18950,22 @@
         <v>790</v>
       </c>
       <c r="B620" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C620" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="C620" s="3" t="s">
+      <c r="D620" s="3" t="s">
         <v>1587</v>
-      </c>
-      <c r="D620" s="3" t="s">
-        <v>1588</v>
       </c>
       <c r="E620" t="s">
         <v>1400</v>
       </c>
       <c r="F620" t="s">
         <v>11</v>
+      </c>
+      <c r="G620">
+        <v>21</v>
       </c>
     </row>
     <row r="621" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -18919,19 +18973,22 @@
         <v>791</v>
       </c>
       <c r="B621" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C621" s="3" t="s">
         <v>1589</v>
       </c>
-      <c r="C621" s="3" t="s">
+      <c r="D621" s="3" t="s">
         <v>1590</v>
-      </c>
-      <c r="D621" s="3" t="s">
-        <v>1591</v>
       </c>
       <c r="E621" t="s">
         <v>70</v>
       </c>
       <c r="F621" t="s">
         <v>11</v>
+      </c>
+      <c r="G621">
+        <v>20</v>
       </c>
     </row>
     <row r="622" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -18939,7 +18996,7 @@
         <v>792</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="C622" s="3" t="s">
         <v>238</v>
@@ -18952,6 +19009,9 @@
       </c>
       <c r="F622" t="s">
         <v>11</v>
+      </c>
+      <c r="G622">
+        <v>21</v>
       </c>
     </row>
     <row r="623" spans="1:7" ht="105" x14ac:dyDescent="0.25">
@@ -18959,19 +19019,22 @@
         <v>794</v>
       </c>
       <c r="B623" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C623" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="C623" s="3" t="s">
+      <c r="D623" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="D623" s="3" t="s">
+      <c r="E623" t="s">
         <v>1595</v>
       </c>
-      <c r="E623" t="s">
-        <v>1596</v>
-      </c>
       <c r="F623" t="s">
         <v>11</v>
+      </c>
+      <c r="G623">
+        <v>20</v>
       </c>
     </row>
     <row r="624" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -18979,7 +19042,7 @@
         <v>795</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="C624" s="3" t="s">
         <v>24</v>
@@ -18992,6 +19055,9 @@
       </c>
       <c r="F624" t="s">
         <v>11</v>
+      </c>
+      <c r="G624">
+        <v>20</v>
       </c>
     </row>
     <row r="625" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -18999,10 +19065,10 @@
         <v>796</v>
       </c>
       <c r="B625" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E625" t="s">
         <v>1598</v>
-      </c>
-      <c r="E625" t="s">
-        <v>1599</v>
       </c>
       <c r="F625" t="s">
         <v>22</v>
@@ -19016,19 +19082,22 @@
         <v>797</v>
       </c>
       <c r="B626" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C626" s="3" t="s">
         <v>1600</v>
       </c>
-      <c r="C626" s="3" t="s">
+      <c r="D626" s="3" t="s">
         <v>1601</v>
-      </c>
-      <c r="D626" s="3" t="s">
-        <v>1602</v>
       </c>
       <c r="E626" t="s">
         <v>440</v>
       </c>
       <c r="F626" t="s">
         <v>11</v>
+      </c>
+      <c r="G626">
+        <v>21</v>
       </c>
     </row>
     <row r="627" spans="1:7" ht="105" x14ac:dyDescent="0.25">
@@ -19036,19 +19105,22 @@
         <v>798</v>
       </c>
       <c r="B627" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C627" s="3" t="s">
         <v>1603</v>
       </c>
-      <c r="C627" s="3" t="s">
+      <c r="D627" s="3" t="s">
         <v>1604</v>
       </c>
-      <c r="D627" s="3" t="s">
+      <c r="E627" t="s">
         <v>1605</v>
       </c>
-      <c r="E627" t="s">
-        <v>1606</v>
-      </c>
       <c r="F627" t="s">
         <v>11</v>
+      </c>
+      <c r="G627">
+        <v>20</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -19056,7 +19128,7 @@
         <v>799</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E628" t="s">
         <v>37</v>
@@ -19073,19 +19145,22 @@
         <v>800</v>
       </c>
       <c r="B629" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C629" s="3" t="s">
         <v>1608</v>
       </c>
-      <c r="C629" s="3" t="s">
+      <c r="D629" s="3" t="s">
         <v>1609</v>
-      </c>
-      <c r="D629" s="3" t="s">
-        <v>1610</v>
       </c>
       <c r="E629" t="s">
         <v>85</v>
       </c>
       <c r="F629" t="s">
         <v>11</v>
+      </c>
+      <c r="G629">
+        <v>21</v>
       </c>
     </row>
     <row r="630" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -19093,19 +19168,22 @@
         <v>801</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="C630" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D630" s="3" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="E630" t="s">
         <v>21</v>
       </c>
       <c r="F630" t="s">
         <v>11</v>
+      </c>
+      <c r="G630">
+        <v>21</v>
       </c>
     </row>
     <row r="631" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19113,7 +19191,7 @@
         <v>804</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="E631" t="s">
         <v>85</v>
@@ -19130,19 +19208,22 @@
         <v>805</v>
       </c>
       <c r="B632" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C632" s="3" t="s">
         <v>1614</v>
       </c>
-      <c r="C632" s="3" t="s">
+      <c r="D632" s="3" t="s">
         <v>1615</v>
       </c>
-      <c r="D632" s="3" t="s">
+      <c r="E632" t="s">
         <v>1616</v>
       </c>
-      <c r="E632" t="s">
-        <v>1617</v>
-      </c>
       <c r="F632" t="s">
         <v>11</v>
+      </c>
+      <c r="G632">
+        <v>20</v>
       </c>
     </row>
     <row r="633" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19150,19 +19231,22 @@
         <v>806</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="C633" s="3" t="s">
         <v>741</v>
       </c>
       <c r="D633" s="3" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="E633" t="s">
         <v>226</v>
       </c>
       <c r="F633" t="s">
         <v>11</v>
+      </c>
+      <c r="G633">
+        <v>20</v>
       </c>
     </row>
     <row r="634" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19170,7 +19254,7 @@
         <v>807</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E634" t="s">
         <v>190</v>
@@ -19187,7 +19271,7 @@
         <v>808</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="E635" t="s">
         <v>435</v>
@@ -19204,7 +19288,7 @@
         <v>809</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="E636" t="s">
         <v>1247</v>
@@ -19221,10 +19305,10 @@
         <v>810</v>
       </c>
       <c r="B637" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C637" s="3" t="s">
         <v>1623</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>1624</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>827</v>
@@ -19234,6 +19318,9 @@
       </c>
       <c r="F637" t="s">
         <v>11</v>
+      </c>
+      <c r="G637">
+        <v>21</v>
       </c>
     </row>
     <row r="638" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19241,10 +19328,10 @@
         <v>812</v>
       </c>
       <c r="B638" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E638" t="s">
         <v>1625</v>
-      </c>
-      <c r="E638" t="s">
-        <v>1626</v>
       </c>
       <c r="F638" t="s">
         <v>22</v>
@@ -19258,19 +19345,22 @@
         <v>814</v>
       </c>
       <c r="B639" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C639" s="3" t="s">
         <v>1627</v>
       </c>
-      <c r="C639" s="3" t="s">
+      <c r="D639" s="3" t="s">
         <v>1628</v>
       </c>
-      <c r="D639" s="3" t="s">
+      <c r="E639" t="s">
         <v>1629</v>
       </c>
-      <c r="E639" t="s">
-        <v>1630</v>
-      </c>
       <c r="F639" t="s">
         <v>11</v>
+      </c>
+      <c r="G639">
+        <v>20</v>
       </c>
     </row>
     <row r="640" spans="1:7" ht="135" x14ac:dyDescent="0.25">
@@ -19278,19 +19368,22 @@
         <v>815</v>
       </c>
       <c r="B640" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C640" s="3" t="s">
         <v>1631</v>
       </c>
-      <c r="C640" s="3" t="s">
+      <c r="D640" s="3" t="s">
         <v>1632</v>
-      </c>
-      <c r="D640" s="3" t="s">
-        <v>1633</v>
       </c>
       <c r="E640" t="s">
         <v>166</v>
       </c>
       <c r="F640" t="s">
         <v>11</v>
+      </c>
+      <c r="G640">
+        <v>20</v>
       </c>
     </row>
     <row r="641" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19298,7 +19391,7 @@
         <v>816</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="C641" s="3" t="s">
         <v>772</v>
@@ -19311,6 +19404,9 @@
       </c>
       <c r="F641" t="s">
         <v>11</v>
+      </c>
+      <c r="G641">
+        <v>20</v>
       </c>
     </row>
     <row r="642" spans="1:7" ht="150" x14ac:dyDescent="0.25">
@@ -19318,19 +19414,22 @@
         <v>817</v>
       </c>
       <c r="B642" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C642" s="3" t="s">
         <v>1635</v>
       </c>
-      <c r="C642" s="3" t="s">
+      <c r="D642" s="3" t="s">
         <v>1636</v>
-      </c>
-      <c r="D642" s="3" t="s">
-        <v>1637</v>
       </c>
       <c r="E642" t="s">
         <v>328</v>
       </c>
       <c r="F642" t="s">
         <v>11</v>
+      </c>
+      <c r="G642">
+        <v>21</v>
       </c>
     </row>
     <row r="643" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -19338,19 +19437,22 @@
         <v>818</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C643" s="3" t="s">
         <v>1466</v>
       </c>
       <c r="D643" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E643" t="s">
         <v>1639</v>
       </c>
-      <c r="E643" t="s">
-        <v>1640</v>
-      </c>
       <c r="F643" t="s">
         <v>11</v>
+      </c>
+      <c r="G643">
+        <v>20</v>
       </c>
     </row>
     <row r="644" spans="1:7" ht="165" x14ac:dyDescent="0.25">
@@ -19358,19 +19460,22 @@
         <v>819</v>
       </c>
       <c r="B644" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C644" s="3" t="s">
         <v>1641</v>
       </c>
-      <c r="C644" s="3" t="s">
+      <c r="D644" s="3" t="s">
         <v>1642</v>
       </c>
-      <c r="D644" s="3" t="s">
+      <c r="E644" t="s">
         <v>1643</v>
       </c>
-      <c r="E644" t="s">
-        <v>1644</v>
-      </c>
       <c r="F644" t="s">
         <v>11</v>
+      </c>
+      <c r="G644">
+        <v>21</v>
       </c>
     </row>
     <row r="645" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19378,7 +19483,7 @@
         <v>820</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="E645" t="s">
         <v>531</v>
@@ -19395,19 +19500,22 @@
         <v>821</v>
       </c>
       <c r="B646" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C646" s="3" t="s">
         <v>1646</v>
       </c>
-      <c r="C646" s="3" t="s">
+      <c r="D646" s="3" t="s">
         <v>1647</v>
       </c>
-      <c r="D646" s="3" t="s">
+      <c r="E646" t="s">
         <v>1648</v>
       </c>
-      <c r="E646" t="s">
-        <v>1649</v>
-      </c>
       <c r="F646" t="s">
         <v>11</v>
+      </c>
+      <c r="G646">
+        <v>20</v>
       </c>
     </row>
     <row r="647" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -19415,19 +19523,22 @@
         <v>822</v>
       </c>
       <c r="B647" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C647" s="3" t="s">
         <v>1650</v>
       </c>
-      <c r="C647" s="3" t="s">
+      <c r="D647" s="3" t="s">
         <v>1651</v>
       </c>
-      <c r="D647" s="3" t="s">
+      <c r="E647" t="s">
         <v>1652</v>
       </c>
-      <c r="E647" t="s">
-        <v>1653</v>
-      </c>
       <c r="F647" t="s">
         <v>11</v>
+      </c>
+      <c r="G647">
+        <v>21</v>
       </c>
     </row>
     <row r="648" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -19435,19 +19546,22 @@
         <v>823</v>
       </c>
       <c r="B648" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C648" s="3" t="s">
         <v>1654</v>
       </c>
-      <c r="C648" s="3" t="s">
+      <c r="D648" s="3" t="s">
         <v>1655</v>
       </c>
-      <c r="D648" s="3" t="s">
+      <c r="E648" t="s">
         <v>1656</v>
       </c>
-      <c r="E648" t="s">
-        <v>1657</v>
-      </c>
       <c r="F648" t="s">
         <v>11</v>
+      </c>
+      <c r="G648">
+        <v>20</v>
       </c>
     </row>
     <row r="649" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19455,10 +19569,10 @@
         <v>825</v>
       </c>
       <c r="B649" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E649" t="s">
         <v>1658</v>
-      </c>
-      <c r="E649" t="s">
-        <v>1659</v>
       </c>
       <c r="F649" t="s">
         <v>22</v>
@@ -19472,19 +19586,22 @@
         <v>826</v>
       </c>
       <c r="B650" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D650" s="3" t="s">
         <v>1660</v>
-      </c>
-      <c r="C650" s="3" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D650" s="3" t="s">
-        <v>1661</v>
       </c>
       <c r="E650" t="s">
         <v>871</v>
       </c>
       <c r="F650" t="s">
         <v>11</v>
+      </c>
+      <c r="G650">
+        <v>21</v>
       </c>
     </row>
     <row r="651" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19492,19 +19609,22 @@
         <v>827</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="C651" s="3" t="s">
         <v>651</v>
       </c>
       <c r="D651" s="3" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E651" t="s">
         <v>26</v>
       </c>
       <c r="F651" t="s">
         <v>11</v>
+      </c>
+      <c r="G651">
+        <v>20</v>
       </c>
     </row>
     <row r="652" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19512,10 +19632,10 @@
         <v>830</v>
       </c>
       <c r="B652" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E652" t="s">
         <v>1664</v>
-      </c>
-      <c r="E652" t="s">
-        <v>1665</v>
       </c>
       <c r="F652" t="s">
         <v>22</v>
@@ -19529,19 +19649,22 @@
         <v>831</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>651</v>
       </c>
       <c r="D653" s="3" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="E653" t="s">
         <v>26</v>
       </c>
       <c r="F653" t="s">
         <v>11</v>
+      </c>
+      <c r="G653">
+        <v>20</v>
       </c>
     </row>
     <row r="654" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -19549,19 +19672,22 @@
         <v>832</v>
       </c>
       <c r="B654" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C654" s="3" t="s">
         <v>1668</v>
       </c>
-      <c r="C654" s="3" t="s">
+      <c r="D654" s="3" t="s">
         <v>1669</v>
-      </c>
-      <c r="D654" s="3" t="s">
-        <v>1670</v>
       </c>
       <c r="E654" t="s">
         <v>15</v>
       </c>
       <c r="F654" t="s">
         <v>11</v>
+      </c>
+      <c r="G654">
+        <v>20</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -19569,7 +19695,7 @@
         <v>833</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="E655" t="s">
         <v>138</v>
@@ -19586,19 +19712,22 @@
         <v>834</v>
       </c>
       <c r="B656" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C656" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="C656" s="3" t="s">
+      <c r="D656" s="3" t="s">
         <v>1673</v>
       </c>
-      <c r="D656" s="3" t="s">
+      <c r="E656" t="s">
         <v>1674</v>
       </c>
-      <c r="E656" t="s">
-        <v>1675</v>
-      </c>
       <c r="F656" t="s">
         <v>11</v>
+      </c>
+      <c r="G656">
+        <v>20</v>
       </c>
     </row>
     <row r="657" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19606,7 +19735,7 @@
         <v>835</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="E657" t="s">
         <v>837</v>
@@ -19623,7 +19752,7 @@
         <v>837</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E658" t="s">
         <v>37</v>
@@ -19640,7 +19769,7 @@
         <v>838</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E659" t="s">
         <v>140</v>
@@ -19657,7 +19786,7 @@
         <v>839</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E660" t="s">
         <v>37</v>
@@ -19674,7 +19803,7 @@
         <v>840</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="C661" s="3" t="s">
         <v>366</v>
@@ -19687,6 +19816,9 @@
       </c>
       <c r="F661" t="s">
         <v>11</v>
+      </c>
+      <c r="G661">
+        <v>20</v>
       </c>
     </row>
     <row r="662" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -19694,19 +19826,22 @@
         <v>841</v>
       </c>
       <c r="B662" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C662" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="C662" s="3" t="s">
+      <c r="D662" s="3" t="s">
         <v>1682</v>
       </c>
-      <c r="D662" s="3" t="s">
+      <c r="E662" t="s">
         <v>1683</v>
       </c>
-      <c r="E662" t="s">
-        <v>1684</v>
-      </c>
       <c r="F662" t="s">
         <v>11</v>
+      </c>
+      <c r="G662">
+        <v>21</v>
       </c>
     </row>
     <row r="663" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19714,10 +19849,10 @@
         <v>842</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E663" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="F663" t="s">
         <v>22</v>
@@ -19731,19 +19866,22 @@
         <v>843</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C664" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D664" s="3" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E664" t="s">
         <v>297</v>
       </c>
       <c r="F664" t="s">
         <v>11</v>
+      </c>
+      <c r="G664">
+        <v>20</v>
       </c>
     </row>
     <row r="665" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -19751,19 +19889,22 @@
         <v>844</v>
       </c>
       <c r="B665" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C665" s="3" t="s">
         <v>1688</v>
       </c>
-      <c r="C665" s="3" t="s">
+      <c r="D665" s="3" t="s">
         <v>1689</v>
-      </c>
-      <c r="D665" s="3" t="s">
-        <v>1690</v>
       </c>
       <c r="E665" t="s">
         <v>283</v>
       </c>
       <c r="F665" t="s">
         <v>11</v>
+      </c>
+      <c r="G665">
+        <v>21</v>
       </c>
     </row>
     <row r="666" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19771,10 +19912,10 @@
         <v>845</v>
       </c>
       <c r="B666" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E666" t="s">
         <v>1691</v>
-      </c>
-      <c r="E666" t="s">
-        <v>1692</v>
       </c>
       <c r="F666" t="s">
         <v>22</v>
@@ -19788,19 +19929,22 @@
         <v>846</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="C667" s="3" t="s">
         <v>712</v>
       </c>
       <c r="D667" s="3" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E667" t="s">
         <v>1481</v>
       </c>
       <c r="F667" t="s">
         <v>11</v>
+      </c>
+      <c r="G667">
+        <v>20</v>
       </c>
     </row>
     <row r="668" spans="1:7" ht="180" x14ac:dyDescent="0.25">
@@ -19808,19 +19952,22 @@
         <v>847</v>
       </c>
       <c r="B668" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C668" s="3" t="s">
         <v>1695</v>
       </c>
-      <c r="C668" s="3" t="s">
+      <c r="D668" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="D668" s="3" t="s">
+      <c r="E668" t="s">
         <v>1697</v>
       </c>
-      <c r="E668" t="s">
-        <v>1698</v>
-      </c>
       <c r="F668" t="s">
         <v>11</v>
+      </c>
+      <c r="G668">
+        <v>20</v>
       </c>
     </row>
     <row r="669" spans="1:7" ht="150" x14ac:dyDescent="0.25">
@@ -19828,19 +19975,22 @@
         <v>848</v>
       </c>
       <c r="B669" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C669" s="3" t="s">
         <v>1699</v>
       </c>
-      <c r="C669" s="3" t="s">
+      <c r="D669" s="3" t="s">
         <v>1700</v>
       </c>
-      <c r="D669" s="3" t="s">
+      <c r="E669" t="s">
         <v>1701</v>
       </c>
-      <c r="E669" t="s">
-        <v>1702</v>
-      </c>
       <c r="F669" t="s">
         <v>11</v>
+      </c>
+      <c r="G669">
+        <v>20</v>
       </c>
     </row>
     <row r="670" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -19848,7 +19998,7 @@
         <v>849</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E670" t="s">
         <v>442</v>
@@ -19865,19 +20015,22 @@
         <v>850</v>
       </c>
       <c r="B671" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C671" s="3" t="s">
         <v>1704</v>
       </c>
-      <c r="C671" s="3" t="s">
+      <c r="D671" s="3" t="s">
         <v>1705</v>
-      </c>
-      <c r="D671" s="3" t="s">
-        <v>1706</v>
       </c>
       <c r="E671" t="s">
         <v>26</v>
       </c>
       <c r="F671" t="s">
         <v>11</v>
+      </c>
+      <c r="G671">
+        <v>20</v>
       </c>
     </row>
     <row r="672" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -19885,19 +20038,22 @@
         <v>851</v>
       </c>
       <c r="B672" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C672" s="3" t="s">
         <v>1707</v>
       </c>
-      <c r="C672" s="3" t="s">
+      <c r="D672" s="3" t="s">
         <v>1708</v>
-      </c>
-      <c r="D672" s="3" t="s">
-        <v>1709</v>
       </c>
       <c r="E672" t="s">
         <v>15</v>
       </c>
       <c r="F672" t="s">
         <v>11</v>
+      </c>
+      <c r="G672">
+        <v>20</v>
       </c>
     </row>
     <row r="673" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -19905,7 +20061,7 @@
         <v>852</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E673" t="s">
         <v>37</v>
@@ -19922,13 +20078,13 @@
         <v>853</v>
       </c>
       <c r="B674" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C674" s="3" t="s">
         <v>1711</v>
       </c>
-      <c r="C674" s="3" t="s">
+      <c r="D674" s="3" t="s">
         <v>1712</v>
-      </c>
-      <c r="D674" s="3" t="s">
-        <v>1713</v>
       </c>
       <c r="E674" t="s">
         <v>1333</v>
@@ -19936,25 +20092,31 @@
       <c r="F674" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="675" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="G674">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>854</v>
       </c>
       <c r="B675" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D675" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="C675" s="3" t="s">
+      <c r="E675" t="s">
         <v>1715</v>
       </c>
-      <c r="D675" s="3" t="s">
-        <v>1716</v>
-      </c>
-      <c r="E675" t="s">
-        <v>1717</v>
-      </c>
       <c r="F675" t="s">
         <v>11</v>
+      </c>
+      <c r="G675">
+        <v>20</v>
       </c>
     </row>
     <row r="676" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -19962,7 +20124,7 @@
         <v>855</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="E676" t="s">
         <v>140</v>
@@ -19979,7 +20141,7 @@
         <v>856</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="E677" t="s">
         <v>105</v>
@@ -19996,7 +20158,7 @@
         <v>857</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="E678" t="s">
         <v>140</v>
@@ -20013,19 +20175,22 @@
         <v>859</v>
       </c>
       <c r="B679" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D679" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="C679" s="3" t="s">
+      <c r="E679" t="s">
         <v>1722</v>
       </c>
-      <c r="D679" s="3" t="s">
-        <v>1723</v>
-      </c>
-      <c r="E679" t="s">
-        <v>1724</v>
-      </c>
       <c r="F679" t="s">
         <v>11</v>
+      </c>
+      <c r="G679">
+        <v>21</v>
       </c>
     </row>
     <row r="680" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -20033,7 +20198,7 @@
         <v>860</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="C680" s="3" t="s">
         <v>502</v>
@@ -20046,6 +20211,9 @@
       </c>
       <c r="F680" t="s">
         <v>11</v>
+      </c>
+      <c r="G680">
+        <v>21</v>
       </c>
     </row>
     <row r="681" spans="1:7" ht="120" x14ac:dyDescent="0.25">
@@ -20053,19 +20221,22 @@
         <v>861</v>
       </c>
       <c r="B681" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D681" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E681" t="s">
         <v>1726</v>
       </c>
-      <c r="C681" s="3" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D681" s="3" t="s">
-        <v>1540</v>
-      </c>
-      <c r="E681" t="s">
-        <v>1728</v>
-      </c>
       <c r="F681" t="s">
         <v>11</v>
+      </c>
+      <c r="G681">
+        <v>20</v>
       </c>
     </row>
     <row r="682" spans="1:7" ht="105" x14ac:dyDescent="0.25">
@@ -20073,39 +20244,45 @@
         <v>862</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="C682" s="3" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>675</v>
       </c>
       <c r="E682" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="F682" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="683" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="G682">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>864</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="C683" s="3" t="s">
-        <v>1733</v>
+        <v>1838</v>
       </c>
       <c r="D683" s="3" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="E683" t="s">
         <v>15</v>
       </c>
       <c r="F683" t="s">
         <v>11</v>
+      </c>
+      <c r="G683">
+        <v>20</v>
       </c>
     </row>
     <row r="684" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -20113,10 +20290,10 @@
         <v>870</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="C684" s="3" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>530</v>
@@ -20126,6 +20303,9 @@
       </c>
       <c r="F684" t="s">
         <v>11</v>
+      </c>
+      <c r="G684">
+        <v>21</v>
       </c>
     </row>
     <row r="685" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -20133,7 +20313,7 @@
         <v>872</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C685" s="3" t="s">
         <v>741</v>
@@ -20146,6 +20326,9 @@
       </c>
       <c r="F685" t="s">
         <v>11</v>
+      </c>
+      <c r="G685">
+        <v>20</v>
       </c>
     </row>
     <row r="686" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -20153,19 +20336,22 @@
         <v>882</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="C686" s="3" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="E686" t="s">
         <v>15</v>
       </c>
       <c r="F686" t="s">
         <v>11</v>
+      </c>
+      <c r="G686">
+        <v>20</v>
       </c>
     </row>
     <row r="687" spans="1:7" ht="165" x14ac:dyDescent="0.25">
@@ -20173,19 +20359,22 @@
         <v>883</v>
       </c>
       <c r="B687" s="3" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="C687" s="3" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="D687" s="3" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="E687" t="s">
         <v>1008</v>
       </c>
       <c r="F687" t="s">
         <v>11</v>
+      </c>
+      <c r="G687">
+        <v>21</v>
       </c>
     </row>
     <row r="688" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -20193,47 +20382,53 @@
         <v>885</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="C688" s="3" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="D688" s="3" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="E688" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="F688" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="689" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G688">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>886</v>
       </c>
       <c r="B689" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D689" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E689" t="s">
         <v>1747</v>
       </c>
-      <c r="C689" s="3" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D689" s="3" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E689" t="s">
-        <v>1750</v>
-      </c>
       <c r="F689" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="690" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G689">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>894</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="C690" s="3" t="s">
         <v>704</v>
@@ -20247,39 +20442,45 @@
       <c r="F690" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="691" spans="1:6" ht="180" x14ac:dyDescent="0.25">
+      <c r="G690">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>898</v>
       </c>
       <c r="B691" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D691" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E691" t="s">
         <v>1752</v>
       </c>
-      <c r="C691" s="3" t="s">
-        <v>1753</v>
-      </c>
-      <c r="D691" s="3" t="s">
-        <v>1754</v>
-      </c>
-      <c r="E691" t="s">
-        <v>1755</v>
-      </c>
       <c r="F691" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="692" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G691">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>902</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="C692" s="3" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="E692" t="s">
         <v>900</v>
@@ -20287,33 +20488,39 @@
       <c r="F692" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="693" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G692">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>910</v>
       </c>
       <c r="B693" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D693" s="3" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E693" t="s">
         <v>1759</v>
       </c>
-      <c r="C693" s="3" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D693" s="3" t="s">
-        <v>1761</v>
-      </c>
-      <c r="E693" t="s">
-        <v>1762</v>
-      </c>
       <c r="F693" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="694" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G693">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>912</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="C694" s="3" t="s">
         <v>561</v>
@@ -20322,24 +20529,27 @@
         <v>50</v>
       </c>
       <c r="E694" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="F694" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="695" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G694">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>913</v>
       </c>
       <c r="B695" s="3" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="C695" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D695" s="3" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="E695" t="s">
         <v>26</v>
@@ -20347,56 +20557,65 @@
       <c r="F695" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="696" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="G695">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" ht="195" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>918</v>
       </c>
       <c r="B696" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D696" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E696" t="s">
         <v>1766</v>
       </c>
-      <c r="C696" s="3" t="s">
-        <v>1767</v>
-      </c>
-      <c r="D696" s="3" t="s">
-        <v>1768</v>
-      </c>
-      <c r="E696" t="s">
-        <v>1769</v>
-      </c>
       <c r="F696" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="697" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G696">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>920</v>
       </c>
       <c r="B697" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D697" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E697" t="s">
         <v>1770</v>
       </c>
-      <c r="C697" s="3" t="s">
-        <v>1771</v>
-      </c>
-      <c r="D697" s="3" t="s">
-        <v>1772</v>
-      </c>
-      <c r="E697" t="s">
-        <v>1773</v>
-      </c>
       <c r="F697" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="698" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G697">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>930</v>
       </c>
       <c r="B698" s="3" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="C698" s="3" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>424</v>
@@ -20407,16 +20626,19 @@
       <c r="F698" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="699" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G698">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>931</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="C699" s="3" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1448</v>
@@ -20427,59 +20649,68 @@
       <c r="F699" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="700" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="G699">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" ht="210" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>932</v>
       </c>
       <c r="B700" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D700" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E700" t="s">
         <v>1778</v>
       </c>
-      <c r="C700" s="3" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D700" s="3" t="s">
-        <v>1780</v>
-      </c>
-      <c r="E700" t="s">
-        <v>1781</v>
-      </c>
       <c r="F700" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="701" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G700">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>933</v>
       </c>
       <c r="B701" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D701" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E701" t="s">
         <v>1782</v>
       </c>
-      <c r="C701" s="3" t="s">
-        <v>1783</v>
-      </c>
-      <c r="D701" s="3" t="s">
-        <v>1784</v>
-      </c>
-      <c r="E701" t="s">
-        <v>1785</v>
-      </c>
       <c r="F701" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="702" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G701">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>937</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="E702" t="s">
         <v>15</v>
@@ -20487,19 +20718,22 @@
       <c r="F702" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="703" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G702">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>940</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="C703" s="3" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
       <c r="D703" s="3" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="E703" t="s">
         <v>26</v>
@@ -20507,16 +20741,19 @@
       <c r="F703" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="704" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G703">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>941</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
       <c r="C704" s="3" t="s">
-        <v>1793</v>
+        <v>1839</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>14</v>
@@ -20526,6 +20763,9 @@
       </c>
       <c r="F704" t="s">
         <v>11</v>
+      </c>
+      <c r="G704">
+        <v>20</v>
       </c>
     </row>
     <row r="705" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -20533,19 +20773,22 @@
         <v>942</v>
       </c>
       <c r="B705" s="3" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="C705" s="3" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="D705" s="3" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
       <c r="E705" t="s">
         <v>15</v>
       </c>
       <c r="F705" t="s">
         <v>11</v>
+      </c>
+      <c r="G705">
+        <v>20</v>
       </c>
     </row>
     <row r="706" spans="1:7" ht="105" x14ac:dyDescent="0.25">
@@ -20553,19 +20796,22 @@
         <v>945</v>
       </c>
       <c r="B706" s="3" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
       <c r="C706" s="3" t="s">
-        <v>1798</v>
+        <v>1794</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="E706" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
       <c r="F706" t="s">
         <v>11</v>
+      </c>
+      <c r="G706">
+        <v>20</v>
       </c>
     </row>
     <row r="707" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -20573,13 +20819,16 @@
         <v>946</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>1801</v>
+        <v>1797</v>
       </c>
       <c r="E707" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="F707" t="s">
         <v>22</v>
+      </c>
+      <c r="G707">
+        <v>1</v>
       </c>
     </row>
     <row r="708" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -20587,19 +20836,22 @@
         <v>956</v>
       </c>
       <c r="B708" s="3" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
       <c r="C708" s="3" t="s">
         <v>550</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
       <c r="E708" t="s">
         <v>15</v>
       </c>
       <c r="F708" t="s">
         <v>11</v>
+      </c>
+      <c r="G708">
+        <v>20</v>
       </c>
     </row>
     <row r="709" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -20607,7 +20859,7 @@
         <v>963</v>
       </c>
       <c r="B709" s="3" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C709" s="3" t="s">
         <v>990</v>
@@ -20620,6 +20872,9 @@
       </c>
       <c r="F709" t="s">
         <v>11</v>
+      </c>
+      <c r="G709">
+        <v>21</v>
       </c>
     </row>
     <row r="710" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -20627,19 +20882,22 @@
         <v>970</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="E710" t="s">
         <v>15</v>
       </c>
       <c r="F710" t="s">
         <v>11</v>
+      </c>
+      <c r="G710">
+        <v>20</v>
       </c>
     </row>
     <row r="711" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -20647,7 +20905,7 @@
         <v>976</v>
       </c>
       <c r="B711" s="3" t="s">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="E711" t="s">
         <v>745</v>
@@ -20664,7 +20922,7 @@
         <v>978</v>
       </c>
       <c r="B712" s="3" t="s">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="E712" t="s">
         <v>21</v>
@@ -20681,19 +20939,22 @@
         <v>979</v>
       </c>
       <c r="B713" s="3" t="s">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="C713" s="3" t="s">
-        <v>1812</v>
+        <v>1808</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="E713" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="F713" t="s">
         <v>11</v>
+      </c>
+      <c r="G713">
+        <v>20</v>
       </c>
     </row>
     <row r="714" spans="1:7" ht="195" x14ac:dyDescent="0.25">
@@ -20701,19 +20962,22 @@
         <v>980</v>
       </c>
       <c r="B714" s="3" t="s">
-        <v>1815</v>
+        <v>1811</v>
       </c>
       <c r="C714" s="3" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="E714" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="F714" t="s">
         <v>11</v>
+      </c>
+      <c r="G714">
+        <v>21</v>
       </c>
     </row>
     <row r="715" spans="1:7" ht="195" x14ac:dyDescent="0.25">
@@ -20721,19 +20985,22 @@
         <v>983</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="C715" s="3" t="s">
-        <v>1820</v>
+        <v>1816</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="E715" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
       <c r="F715" t="s">
         <v>11</v>
+      </c>
+      <c r="G715">
+        <v>21</v>
       </c>
     </row>
     <row r="716" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -20741,7 +21008,7 @@
         <v>986</v>
       </c>
       <c r="B716" s="3" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="E716" t="s">
         <v>26</v>
@@ -20758,7 +21025,7 @@
         <v>987</v>
       </c>
       <c r="B717" s="3" t="s">
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="E717" t="s">
         <v>37</v>
@@ -20775,7 +21042,7 @@
         <v>991</v>
       </c>
       <c r="B718" s="3" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="C718" s="3" t="s">
         <v>61</v>
@@ -20788,6 +21055,9 @@
       </c>
       <c r="F718" t="s">
         <v>11</v>
+      </c>
+      <c r="G718">
+        <v>21</v>
       </c>
     </row>
     <row r="719" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -20795,19 +21065,22 @@
         <v>996</v>
       </c>
       <c r="B719" s="3" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
       <c r="C719" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="E719" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="F719" t="s">
         <v>11</v>
+      </c>
+      <c r="G719">
+        <v>21</v>
       </c>
     </row>
     <row r="720" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -20815,19 +21088,22 @@
         <v>1004</v>
       </c>
       <c r="B720" s="3" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="C720" s="3" t="s">
         <v>188</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="E720" t="s">
         <v>531</v>
       </c>
       <c r="F720" t="s">
         <v>11</v>
+      </c>
+      <c r="G720">
+        <v>20</v>
       </c>
     </row>
     <row r="721" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -20835,10 +21111,10 @@
         <v>1005</v>
       </c>
       <c r="B721" s="3" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="E721" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
       <c r="F721" t="s">
         <v>22</v>
@@ -20852,10 +21128,10 @@
         <v>1006</v>
       </c>
       <c r="B722" s="3" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="C722" s="3" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1230</v>
@@ -20866,11 +21142,8 @@
       <c r="F722" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G724">
-        <f>SUM(G584:G722)</f>
-        <v>103</v>
+      <c r="G722">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
